--- a/st.xlsx
+++ b/st.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abumurad/Library/Group Containers/UBF8T346G9.Office/User Content.localized/Templates.localized/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abumurad/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95435FA0-FF76-164F-9843-37A657A5906E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3C6096E-2579-BF47-B4EC-1521B831291A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{C0AB6810-C611-244D-B299-5FF1576DCFAF}"/>
   </bookViews>
@@ -29,6 +29,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="379">
   <si>
     <t>رقم الهويه</t>
   </si>
@@ -1043,9 +1044,6 @@
     <t>اللجنة التاسعة</t>
   </si>
   <si>
-    <t xml:space="preserve">ثالث ثانوي عام  [ أ ] </t>
-  </si>
-  <si>
     <t xml:space="preserve">لميس بنت احمد بن غرم الله ال سعيد </t>
   </si>
   <si>
@@ -1154,7 +1152,25 @@
     <t>اللجنة العاشرة</t>
   </si>
   <si>
-    <t xml:space="preserve">ثالث ثانوي عام  [ ب ] </t>
+    <t>ثاني ثانوي شرعي</t>
+  </si>
+  <si>
+    <t>ثثاني ثانوي شرعي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثاني ثانوي شرعي </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثالث ثانوي صحة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثثالث ثانوي صحة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثالث ثانوي صحة  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثثالث ثانوي صحة  </t>
   </si>
   <si>
     <t>إعداد الأستاذة/ فاطمة ناجي عبدالعزيز ال سرحان</t>
@@ -1769,81 +1785,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1907,6 +1848,24 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1933,6 +1892,63 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1961,8 +1977,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>151501</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1257299</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>469900</xdr:rowOff>
     </xdr:to>
@@ -2245,7 +2261,7 @@
               <a:effectLst/>
               <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>المملكة العربية السعودية</a:t>
           </a:r>
@@ -2263,7 +2279,7 @@
               <a:effectLst/>
               <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>وزارة التعليم</a:t>
           </a:r>
@@ -2281,7 +2297,7 @@
               <a:effectLst/>
               <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>إدارة التعليم بمنطقة الباحه</a:t>
           </a:r>
@@ -2299,7 +2315,7 @@
               <a:effectLst/>
               <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>ثانوية السيدة</a:t>
           </a:r>
@@ -2308,7 +2324,7 @@
               <a:effectLst/>
               <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t> فاطمة الزهراء بالباحة</a:t>
           </a:r>
@@ -2316,7 +2332,7 @@
             <a:effectLst/>
             <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             <a:ea typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            <a:cs typeface="+mn-cs"/>
+            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2703,9 +2719,9 @@
   <dimension ref="A1:I339"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2" defaultRowHeight="25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="11" hidden="1" customWidth="1"/>
-    <col min="3" max="8" width="19" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" customWidth="1"/>
+    <col min="3" max="8" width="19" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.7109375" style="4"/>
   </cols>
   <sheetData>
@@ -9654,7 +9670,7 @@
         <v>334</v>
       </c>
       <c r="H269" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9680,7 +9696,7 @@
         <v>334</v>
       </c>
       <c r="H270" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9706,7 +9722,7 @@
         <v>334</v>
       </c>
       <c r="H271" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="272" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9732,7 +9748,7 @@
         <v>334</v>
       </c>
       <c r="H272" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9758,7 +9774,7 @@
         <v>334</v>
       </c>
       <c r="H273" s="35" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
     </row>
     <row r="274" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9784,7 +9800,7 @@
         <v>334</v>
       </c>
       <c r="H274" s="34" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9810,7 +9826,7 @@
         <v>334</v>
       </c>
       <c r="H275" s="35" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9836,7 +9852,7 @@
         <v>334</v>
       </c>
       <c r="H276" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9862,7 +9878,7 @@
         <v>334</v>
       </c>
       <c r="H277" s="35" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="278" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9888,7 +9904,7 @@
         <v>334</v>
       </c>
       <c r="H278" s="34" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9914,7 +9930,7 @@
         <v>334</v>
       </c>
       <c r="H279" s="35" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9940,7 +9956,7 @@
         <v>334</v>
       </c>
       <c r="H280" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9966,7 +9982,7 @@
         <v>334</v>
       </c>
       <c r="H281" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -9992,7 +10008,7 @@
         <v>334</v>
       </c>
       <c r="H282" s="34" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10018,7 +10034,7 @@
         <v>334</v>
       </c>
       <c r="H283" s="35" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="284" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10044,7 +10060,7 @@
         <v>334</v>
       </c>
       <c r="H284" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="285" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10070,7 +10086,7 @@
         <v>334</v>
       </c>
       <c r="H285" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="286" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10096,7 +10112,7 @@
         <v>334</v>
       </c>
       <c r="H286" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="287" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10122,7 +10138,7 @@
         <v>334</v>
       </c>
       <c r="H287" s="35" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="288" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10148,7 +10164,7 @@
         <v>334</v>
       </c>
       <c r="H288" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="289" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10174,7 +10190,7 @@
         <v>334</v>
       </c>
       <c r="H289" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="290" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10200,7 +10216,7 @@
         <v>334</v>
       </c>
       <c r="H290" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="291" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10226,7 +10242,7 @@
         <v>334</v>
       </c>
       <c r="H291" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="292" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10252,7 +10268,7 @@
         <v>334</v>
       </c>
       <c r="H292" s="34" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="293" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10278,7 +10294,7 @@
         <v>334</v>
       </c>
       <c r="H293" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="294" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10304,7 +10320,7 @@
         <v>334</v>
       </c>
       <c r="H294" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="295" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10330,7 +10346,7 @@
         <v>334</v>
       </c>
       <c r="H295" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="296" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10356,7 +10372,7 @@
         <v>334</v>
       </c>
       <c r="H296" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="297" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10382,7 +10398,7 @@
         <v>334</v>
       </c>
       <c r="H297" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="298" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10408,7 +10424,7 @@
         <v>334</v>
       </c>
       <c r="H298" s="34" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="299" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10434,7 +10450,7 @@
         <v>334</v>
       </c>
       <c r="H299" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="300" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10445,7 +10461,7 @@
         <v>1142595485</v>
       </c>
       <c r="C300" s="23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D300" s="37" t="s">
         <v>32</v>
@@ -10460,7 +10476,7 @@
         <v>334</v>
       </c>
       <c r="H300" s="34" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="301" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10486,7 +10502,7 @@
         <v>334</v>
       </c>
       <c r="H301" s="35" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="302" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10497,7 +10513,7 @@
         <v>1152404644</v>
       </c>
       <c r="C302" s="23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D302" s="36" t="s">
         <v>30</v>
@@ -10509,10 +10525,10 @@
         <v>111450113</v>
       </c>
       <c r="G302" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H302" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="303" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10523,7 +10539,7 @@
         <v>1172821744</v>
       </c>
       <c r="C303" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D303" s="37" t="s">
         <v>30</v>
@@ -10535,10 +10551,10 @@
         <v>111450114</v>
       </c>
       <c r="G303" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H303" s="35" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="304" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10549,7 +10565,7 @@
         <v>1153421969</v>
       </c>
       <c r="C304" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D304" s="37" t="s">
         <v>30</v>
@@ -10561,10 +10577,10 @@
         <v>111450115</v>
       </c>
       <c r="G304" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H304" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="305" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10575,7 +10591,7 @@
         <v>1166935369</v>
       </c>
       <c r="C305" s="23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D305" s="37" t="s">
         <v>30</v>
@@ -10587,10 +10603,10 @@
         <v>111450116</v>
       </c>
       <c r="G305" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H305" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="306" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10601,7 +10617,7 @@
         <v>1150591848</v>
       </c>
       <c r="C306" s="23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D306" s="37" t="s">
         <v>30</v>
@@ -10613,10 +10629,10 @@
         <v>111450117</v>
       </c>
       <c r="G306" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H306" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="307" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10627,7 +10643,7 @@
         <v>1168041638</v>
       </c>
       <c r="C307" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D307" s="37" t="s">
         <v>30</v>
@@ -10639,10 +10655,10 @@
         <v>111450118</v>
       </c>
       <c r="G307" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H307" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="308" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10653,7 +10669,7 @@
         <v>1154376782</v>
       </c>
       <c r="C308" s="23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D308" s="37" t="s">
         <v>30</v>
@@ -10665,10 +10681,10 @@
         <v>111450119</v>
       </c>
       <c r="G308" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H308" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="309" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10679,7 +10695,7 @@
         <v>2273641569</v>
       </c>
       <c r="C309" s="23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D309" s="37" t="s">
         <v>30</v>
@@ -10691,10 +10707,10 @@
         <v>111450120</v>
       </c>
       <c r="G309" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H309" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="310" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10705,7 +10721,7 @@
         <v>1149537308</v>
       </c>
       <c r="C310" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D310" s="37" t="s">
         <v>30</v>
@@ -10717,10 +10733,10 @@
         <v>111450121</v>
       </c>
       <c r="G310" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H310" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="311" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10731,7 +10747,7 @@
         <v>1153309792</v>
       </c>
       <c r="C311" s="23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D311" s="37" t="s">
         <v>30</v>
@@ -10743,10 +10759,10 @@
         <v>111450122</v>
       </c>
       <c r="G311" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H311" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="312" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10757,7 +10773,7 @@
         <v>1159570256</v>
       </c>
       <c r="C312" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D312" s="37" t="s">
         <v>30</v>
@@ -10769,10 +10785,10 @@
         <v>111450123</v>
       </c>
       <c r="G312" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H312" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="313" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10783,7 +10799,7 @@
         <v>1150984316</v>
       </c>
       <c r="C313" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D313" s="37" t="s">
         <v>30</v>
@@ -10795,10 +10811,10 @@
         <v>111450124</v>
       </c>
       <c r="G313" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H313" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="314" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10809,7 +10825,7 @@
         <v>1037131271</v>
       </c>
       <c r="C314" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D314" s="37" t="s">
         <v>30</v>
@@ -10821,10 +10837,10 @@
         <v>111450126</v>
       </c>
       <c r="G314" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H314" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="315" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10835,7 +10851,7 @@
         <v>1069392791</v>
       </c>
       <c r="C315" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D315" s="37" t="s">
         <v>31</v>
@@ -10847,10 +10863,10 @@
         <v>121600064</v>
       </c>
       <c r="G315" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H315" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="316" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10861,7 +10877,7 @@
         <v>2367933468</v>
       </c>
       <c r="C316" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D316" s="37" t="s">
         <v>31</v>
@@ -10873,10 +10889,10 @@
         <v>121600065</v>
       </c>
       <c r="G316" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H316" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="317" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10887,7 +10903,7 @@
         <v>1038678148</v>
       </c>
       <c r="C317" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D317" s="37" t="s">
         <v>31</v>
@@ -10899,10 +10915,10 @@
         <v>121600066</v>
       </c>
       <c r="G317" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H317" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="318" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10913,7 +10929,7 @@
         <v>2305374577</v>
       </c>
       <c r="C318" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D318" s="37" t="s">
         <v>31</v>
@@ -10925,10 +10941,10 @@
         <v>121600083</v>
       </c>
       <c r="G318" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H318" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="319" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10939,7 +10955,7 @@
         <v>1147934101</v>
       </c>
       <c r="C319" s="23" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D319" s="37" t="s">
         <v>31</v>
@@ -10951,10 +10967,10 @@
         <v>121600084</v>
       </c>
       <c r="G319" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H319" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="320" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10965,7 +10981,7 @@
         <v>1146150667</v>
       </c>
       <c r="C320" s="23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D320" s="37" t="s">
         <v>31</v>
@@ -10977,10 +10993,10 @@
         <v>121600085</v>
       </c>
       <c r="G320" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H320" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="321" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -10991,7 +11007,7 @@
         <v>2293558835</v>
       </c>
       <c r="C321" s="23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D321" s="37" t="s">
         <v>31</v>
@@ -11003,10 +11019,10 @@
         <v>121600086</v>
       </c>
       <c r="G321" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H321" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="322" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11017,7 +11033,7 @@
         <v>2352617704</v>
       </c>
       <c r="C322" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D322" s="37" t="s">
         <v>31</v>
@@ -11029,10 +11045,10 @@
         <v>121600087</v>
       </c>
       <c r="G322" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H322" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="323" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11043,7 +11059,7 @@
         <v>214371000</v>
       </c>
       <c r="C323" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D323" s="37" t="s">
         <v>31</v>
@@ -11055,10 +11071,10 @@
         <v>121600088</v>
       </c>
       <c r="G323" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H323" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="324" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11069,7 +11085,7 @@
         <v>1140871839</v>
       </c>
       <c r="C324" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D324" s="37" t="s">
         <v>32</v>
@@ -11081,10 +11097,10 @@
         <v>131600063</v>
       </c>
       <c r="G324" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H324" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="325" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11095,7 +11111,7 @@
         <v>1159570207</v>
       </c>
       <c r="C325" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D325" s="37" t="s">
         <v>32</v>
@@ -11107,10 +11123,10 @@
         <v>131600064</v>
       </c>
       <c r="G325" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H325" s="35" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="326" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11121,7 +11137,7 @@
         <v>1139325599</v>
       </c>
       <c r="C326" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D326" s="37" t="s">
         <v>32</v>
@@ -11133,10 +11149,10 @@
         <v>131600065</v>
       </c>
       <c r="G326" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H326" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="327" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11147,7 +11163,7 @@
         <v>1143917076</v>
       </c>
       <c r="C327" s="23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D327" s="37" t="s">
         <v>32</v>
@@ -11159,10 +11175,10 @@
         <v>131600066</v>
       </c>
       <c r="G327" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H327" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="328" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11173,7 +11189,7 @@
         <v>1124425156</v>
       </c>
       <c r="C328" s="23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D328" s="37" t="s">
         <v>32</v>
@@ -11185,10 +11201,10 @@
         <v>131600067</v>
       </c>
       <c r="G328" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H328" s="34" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="329" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11199,7 +11215,7 @@
         <v>1037856455</v>
       </c>
       <c r="C329" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D329" s="37" t="s">
         <v>32</v>
@@ -11211,10 +11227,10 @@
         <v>131600068</v>
       </c>
       <c r="G329" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H329" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="330" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11225,7 +11241,7 @@
         <v>1051492955</v>
       </c>
       <c r="C330" s="23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D330" s="37" t="s">
         <v>32</v>
@@ -11237,10 +11253,10 @@
         <v>131600069</v>
       </c>
       <c r="G330" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H330" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="331" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11251,7 +11267,7 @@
         <v>1100424926</v>
       </c>
       <c r="C331" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D331" s="37" t="s">
         <v>32</v>
@@ -11263,10 +11279,10 @@
         <v>131600070</v>
       </c>
       <c r="G331" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H331" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11277,7 +11293,7 @@
         <v>1010671509</v>
       </c>
       <c r="C332" s="23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D332" s="37" t="s">
         <v>32</v>
@@ -11289,10 +11305,10 @@
         <v>131600071</v>
       </c>
       <c r="G332" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H332" s="34" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="333" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11303,7 +11319,7 @@
         <v>1082101559</v>
       </c>
       <c r="C333" s="23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D333" s="37" t="s">
         <v>32</v>
@@ -11315,10 +11331,10 @@
         <v>131600072</v>
       </c>
       <c r="G333" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H333" s="35" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="334" spans="1:8" ht="25" customHeight="1" thickBot="1">
@@ -11329,7 +11345,7 @@
         <v>1018935328</v>
       </c>
       <c r="C334" s="23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D334" s="37" t="s">
         <v>32</v>
@@ -11341,10 +11357,10 @@
         <v>131600073</v>
       </c>
       <c r="G334" s="41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H334" s="42" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="335" spans="1:8" ht="25" customHeight="1">
@@ -11359,7 +11375,7 @@
     </row>
     <row r="336" spans="1:8" ht="25" customHeight="1">
       <c r="A336" s="49" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B336" s="45"/>
       <c r="C336" s="45"/>
@@ -11402,7 +11418,7 @@
       <c r="H339" s="48"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="A90uQ2JB31moG2ROk4nnQbmqSj9v0G4kqUc866hK/BM9vTiep3yaYjEjKKMwbhWBhHkSA70jeMb9tiP11liGww==" saltValue="bkVWgYzx135+NKMRbj75Aw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ptERC3gezJeTBBQh1gEPjvE2cxcpdwKXnrFIRLXPE/f9HrMkv3ziRPfvG45RfWyD6FTU1VUTC1CLCFbFXvIOyA==" saltValue="DHknO5jlvXz0xjjm1Do7/w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A3:H3"/>
@@ -11428,29 +11444,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="66" customHeight="1">
-      <c r="A1" s="51"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="54"/>
+      <c r="A1" s="87"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="90"/>
       <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" ht="66" customHeight="1">
-      <c r="A2" s="53"/>
+      <c r="A2" s="89"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="43"/>
       <c r="E2" s="43"/>
       <c r="F2" s="43"/>
       <c r="G2" s="43"/>
-      <c r="H2" s="55"/>
+      <c r="H2" s="91"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="66" customHeight="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="92" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="44"/>
@@ -11459,7 +11475,7 @@
       <c r="E3" s="44"/>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
-      <c r="H3" s="57"/>
+      <c r="H3" s="93"/>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="17" thickBot="1">
@@ -11473,36 +11489,36 @@
       <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:9" ht="16" customHeight="1">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="59"/>
+      <c r="B5" s="73"/>
       <c r="C5" s="14"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="66"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="96"/>
     </row>
     <row r="6" spans="1:9" ht="16" customHeight="1">
-      <c r="A6" s="60"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="75"/>
       <c r="C6" s="14"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="99"/>
     </row>
     <row r="7" spans="1:9" ht="17" customHeight="1" thickBot="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="102"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="13"/>
@@ -11525,74 +11541,74 @@
       <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:9" ht="16" customHeight="1">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="59"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
-      <c r="E10" s="94" t="s">
+      <c r="E10" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="96"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="80"/>
     </row>
     <row r="11" spans="1:9" ht="16" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="61"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="99"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="83"/>
     </row>
     <row r="12" spans="1:9" ht="17" customHeight="1" thickBot="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="102"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="86"/>
     </row>
     <row r="13" spans="1:9" ht="16" customHeight="1">
-      <c r="A13" s="79" t="e">
+      <c r="A13" s="57" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="B13" s="80"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="85" t="e">
+      <c r="E13" s="63" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,3,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="87"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="65"/>
     </row>
     <row r="14" spans="1:9" ht="16" customHeight="1">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="90"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="68"/>
     </row>
     <row r="15" spans="1:9" ht="17" customHeight="1" thickBot="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="62"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="93"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="71"/>
     </row>
     <row r="16" spans="1:9" ht="17" thickBot="1">
       <c r="A16" s="13"/>
@@ -11605,74 +11621,74 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="94" t="s">
+      <c r="E17" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="96"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="80"/>
     </row>
     <row r="18" spans="1:8" ht="16" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="99"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="83"/>
     </row>
     <row r="19" spans="1:8" ht="16" customHeight="1" thickBot="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="77"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="102"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="86"/>
     </row>
     <row r="20" spans="1:8" ht="16" customHeight="1">
-      <c r="A20" s="79" t="e">
+      <c r="A20" s="57" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,4,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="B20" s="80"/>
+      <c r="B20" s="58"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="85" t="e">
+      <c r="E20" s="63" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,5,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="65"/>
     </row>
     <row r="21" spans="1:8" ht="16" customHeight="1">
-      <c r="A21" s="81"/>
-      <c r="B21" s="82"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="60"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="90"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="68"/>
     </row>
     <row r="22" spans="1:8" ht="16" customHeight="1" thickBot="1">
-      <c r="A22" s="83"/>
-      <c r="B22" s="84"/>
+      <c r="A22" s="61"/>
+      <c r="B22" s="62"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="93"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="71"/>
     </row>
     <row r="23" spans="1:8" ht="17" thickBot="1">
       <c r="A23" s="13"/>
@@ -11685,74 +11701,74 @@
       <c r="H23" s="15"/>
     </row>
     <row r="24" spans="1:8" ht="16" customHeight="1">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="73"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="94" t="s">
+      <c r="E24" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="96"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="80"/>
     </row>
     <row r="25" spans="1:8" ht="16" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="75"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="98"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="99"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="83"/>
     </row>
     <row r="26" spans="1:8" ht="17" customHeight="1" thickBot="1">
-      <c r="A26" s="62"/>
-      <c r="B26" s="63"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="77"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="102"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="85"/>
+      <c r="H26" s="86"/>
     </row>
     <row r="27" spans="1:8" ht="16" customHeight="1">
-      <c r="A27" s="79" t="e">
+      <c r="A27" s="57" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,6,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="B27" s="80"/>
+      <c r="B27" s="58"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
-      <c r="E27" s="85" t="e">
+      <c r="E27" s="63" t="e">
         <f>VLOOKUP($D$5,القاعده!$B$4:$H$334,7,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="87"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="65"/>
     </row>
     <row r="28" spans="1:8" ht="16" customHeight="1">
-      <c r="A28" s="81"/>
-      <c r="B28" s="82"/>
+      <c r="A28" s="59"/>
+      <c r="B28" s="60"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="90"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="68"/>
     </row>
     <row r="29" spans="1:8" ht="17" customHeight="1" thickBot="1">
-      <c r="A29" s="83"/>
-      <c r="B29" s="84"/>
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="93"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="71"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="13"/>
@@ -11795,52 +11811,57 @@
       <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="73" t="s">
-        <v>373</v>
-      </c>
-      <c r="B34" s="74"/>
+      <c r="A34" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="B34" s="52"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
-      <c r="F34" s="74" t="s">
+      <c r="F34" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="74"/>
-      <c r="H34" s="77"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="55"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="73"/>
-      <c r="B35" s="74"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="77"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="55"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="73"/>
-      <c r="B36" s="74"/>
+      <c r="A36" s="51"/>
+      <c r="B36" s="52"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="77"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="55"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="75"/>
-      <c r="B37" s="76"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="78"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="56"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IGmD356GLxLXjW5Xm8y+tWKK/YRwQ7euzQjRCqkSLyFWDaLgk6yE+VWq4qwK2uyDdGP9K7GbjHyYYNqZr9LpBQ==" saltValue="pCKFQN1r8qaISQUKhm8AqQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hfaoQ+ZsuwMfD3HH2qkeT2vbUJABttpM5tLM7NgeoUtDTABPNaqDSg0FclqyqUIE8EbVl4+Rgz56djiOWvHzOA==" saltValue="pTpPYT3Vgu0o9nH2idsIAA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="19">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="D5:H7"/>
     <mergeCell ref="A34:B37"/>
     <mergeCell ref="F34:H37"/>
     <mergeCell ref="A27:B29"/>
@@ -11855,11 +11876,6 @@
     <mergeCell ref="E13:H15"/>
     <mergeCell ref="A20:B22"/>
     <mergeCell ref="E20:H22"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="D5:H7"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.75" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
